--- a/artfynd/A 49808-2023 artfynd.xlsx
+++ b/artfynd/A 49808-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 49808-2023 artfynd.xlsx
+++ b/artfynd/A 49808-2023 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>131732263</v>
       </c>
       <c r="B3" t="n">
-        <v>104135</v>
+        <v>104138</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 49808-2023 artfynd.xlsx
+++ b/artfynd/A 49808-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96406354</v>
+        <v>131732263</v>
       </c>
       <c r="B2" t="n">
-        <v>106964</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104239</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220299</v>
+        <v>706</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Svedjenäva</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Geranium bohemicum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,24 +703,36 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Herrgölet 400m o, Srm</t>
+          <t>Herrgölet NO om , Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>606458.5713921534</v>
+        <v>606100</v>
       </c>
       <c r="R2" t="n">
-        <v>6553416.056273011</v>
+        <v>6553540</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,22 +756,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-09-22</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-09-22</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,9 +774,14 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Skogsväg</t>
+          <t>hygge</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -797,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131732263</v>
+        <v>96406354</v>
       </c>
       <c r="B3" t="n">
-        <v>104138</v>
+        <v>110078</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,16 +810,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>706</v>
+        <v>220299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svedjenäva</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Geranium bohemicum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -825,36 +827,24 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Herrgölet NO om , Srm</t>
+          <t>Herrgölet 400m o, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>606100</v>
+        <v>606459</v>
       </c>
       <c r="R3" t="n">
-        <v>6553540</v>
+        <v>6553416</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -878,12 +868,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2021-09-22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2021-09-22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,14 +886,9 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>hygge</t>
+          <t>Skogsväg</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -918,6 +903,224 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>86944378</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Djurgården 350 m NNO, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>605663</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6553426</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hyltinge</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2020-07-16</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2020-07-16</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Kraftledningsgata</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>86944370</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99036</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Djurgården 350 m NNO, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>605663</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6553426</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hyltinge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2020-07-16</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2020-07-16</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Kraftledningsgata</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 49808-2023 artfynd.xlsx
+++ b/artfynd/A 49808-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -796,6 +801,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131732263</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -903,6 +913,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96406354</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1010,6 +1025,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86944378</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1121,8 +1141,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86944370</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>